--- a/public/datos/4.1_Matriz_procesos.xlsx
+++ b/public/datos/4.1_Matriz_procesos.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Matriz_Procesos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Procesos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Responsables" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Documentos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Indicadores" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Enunciado_Caso" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Matriz_Caracterizacion" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Procesos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Responsables" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Inventario_Documentos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Catalogo_Indicadores" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,166 +430,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Código</t>
+          <t>Sección</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Proceso</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Documentos asociados</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Indicador</t>
+          <t>Detalle del Requerimiento / Parámetros del Caso</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PE-01</t>
+          <t>Código de Actividad</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Direccionamiento estratégico</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PE-02</t>
+          <t>Título del Caso</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gestión de la calidad</t>
+          <t>Matriz maestra de caracterización e interacción de procesos SIG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PM-01</t>
+          <t>Organización</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Producción</t>
+          <t>Lácteos del Caribe S.A.S. - Sistema Integrado de Gestión</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PM-02</t>
+          <t>1. Situación Problema</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Comercial y ventas</t>
+          <t>Para la auditoría de renovación ISO 9001, Bureau Veritas exige el Mapa de Interacción y Caracterización de Procesos con responsables, cobertura documental e indicadores.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PM-03</t>
+          <t>2. Misión del Aprendiz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Logística y distribución</t>
+          <t>Integrar en Matriz_Caracterizacion los 10 procesos corporativos desde 4 fuentes, calculando cobertura documental con CONTAR.SI y alertando procesos sin documentación.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PA-01</t>
+          <t>Requerimiento 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Talento humano</t>
+          <t>Cruce de Responsable: Traer el Líder oficial desde Maestro_Responsables con BUSCARV o BUSCARX.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PA-02</t>
+          <t>Requerimiento 2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Compras</t>
+          <t>Cobertura Documental: Contar los documentos reales de cada proceso con =CONTAR.SI(Inventario_Documentos!$C$2:$C$50; Codigo_Proceso).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PA-03</t>
+          <t>Requerimiento 3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mantenimiento</t>
+          <t>Indicador Asignado: Vincular el indicador principal desde Catalogo_Indicadores con BUSCARV.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PA-04</t>
+          <t>Requerimiento 4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Seguridad y salud en el trabajo</t>
+          <t>Alerta Condicional: Configurar formato condicional con fórmula (=$E2=0) para resaltar en rojo cualquier proceso con 0 documentos (Gestión Ambiental).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PA-05</t>
+          <t>Dificultad Clave / Regla Técnica</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gestión ambiental</t>
+          <t>Articula las cuatro hojas sin romper las referencias relativas ni perder la sincronización al filtrar procesos.</t>
         </is>
       </c>
     </row>
@@ -598,6 +575,236 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Proceso</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de Proceso</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Responsable Líder</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Documentos Asociados (=CONTAR.SI)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Indicador Principal</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Alerta Cobertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PE-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Direccionamiento estratégico</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Estratégico</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PE-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Gestión de la calidad</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Estratégico</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PM-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Producción</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Misional</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PM-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Comercial y ventas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Misional</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PM-03</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Logística y distribución</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Misional</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PA-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Talento humano</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PA-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Compras</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PA-03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PA-04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Seguridad y salud en el trabajo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PA-05</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Gestión ambiental</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -855,7 +1062,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1073,7 +1280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1789,7 +1996,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
